--- a/divFME/ages/nya_ages/common_tabeller.xlsx
+++ b/divFME/ages/nya_ages/common_tabeller.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\kix\divFME\ages\nya_ages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40001_{F56D1F63-F1C2-43D4-A6E5-F4DDB9EFF13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEACD3D4-ABB9-468E-8C3F-9077373895E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="koordsys" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -179,9 +176,6 @@
     <t>RT90 0 gon 0:-15</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>sys_uri</t>
   </si>
   <si>
@@ -260,9 +254,6 @@
     <t>Shape</t>
   </si>
   <si>
-    <t>description</t>
-  </si>
-  <si>
     <t>Riksantikvarieämbetets arkeologiska uppdragsverksamhet</t>
   </si>
   <si>
@@ -611,13 +602,19 @@
     <t>org_uri</t>
   </si>
   <si>
-    <t>epsg_kod</t>
+    <t>epsg</t>
+  </si>
+  <si>
+    <t>namn</t>
+  </si>
+  <si>
+    <t>beskrivning</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -673,9 +670,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -713,7 +710,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -819,7 +816,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -961,14 +958,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -979,16 +976,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" t="s">
         <v>46</v>
-      </c>
-      <c r="C1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1002,7 +999,7 @@
         <v>3006</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1016,7 +1013,7 @@
         <v>3007</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1030,7 +1027,7 @@
         <v>3008</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1044,7 +1041,7 @@
         <v>3009</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1058,7 +1055,7 @@
         <v>3010</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1072,7 +1069,7 @@
         <v>3011</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1086,7 +1083,7 @@
         <v>3012</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1100,7 +1097,7 @@
         <v>3013</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1114,7 +1111,7 @@
         <v>3014</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1128,7 +1125,7 @@
         <v>3015</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1142,7 +1139,7 @@
         <v>3016</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,7 +1153,7 @@
         <v>3017</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1170,7 +1167,7 @@
         <v>3018</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1184,7 +1181,7 @@
         <v>3019</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1198,7 +1195,7 @@
         <v>3020</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1212,7 +1209,7 @@
         <v>3021</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1226,7 +1223,7 @@
         <v>3022</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1240,7 +1237,7 @@
         <v>3023</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1254,7 +1251,7 @@
         <v>3024</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1656,7 +1653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1666,13 +1663,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>189</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1680,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1688,7 +1685,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1696,7 +1693,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1704,7 +1701,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1712,7 +1709,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1721,7 +1718,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1730,13 +1727,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>189</v>
       </c>
       <c r="C1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1744,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1752,7 +1749,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1760,7 +1757,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1768,7 +1765,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1776,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1784,7 +1781,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1792,7 +1789,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1800,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1808,7 +1805,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1816,7 +1813,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1824,7 +1821,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1832,7 +1829,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1840,7 +1837,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1848,7 +1845,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1856,7 +1853,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1864,7 +1861,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1872,7 +1869,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1880,7 +1877,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1888,7 +1885,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1896,7 +1893,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1904,7 +1901,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1912,7 +1909,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1920,7 +1917,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1928,7 +1925,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1936,7 +1933,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1944,7 +1941,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1952,7 +1949,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1960,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1968,7 +1965,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1976,7 +1973,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1984,7 +1981,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1992,7 +1989,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2000,7 +1997,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2008,7 +2005,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2016,7 +2013,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2024,7 +2021,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2032,7 +2029,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2040,7 +2037,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2048,7 +2045,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2056,7 +2053,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2064,7 +2061,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2072,7 +2069,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2080,7 +2077,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2088,7 +2085,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2096,7 +2093,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2104,7 +2101,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2112,7 +2109,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2120,7 +2117,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2128,7 +2125,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2136,7 +2133,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2144,7 +2141,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2152,7 +2149,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2160,7 +2157,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2168,7 +2165,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2176,7 +2173,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2184,7 +2181,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2192,7 +2189,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2200,7 +2197,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2208,7 +2205,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2216,7 +2213,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2224,7 +2221,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2232,7 +2229,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2240,7 +2237,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2248,7 +2245,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2256,7 +2253,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -2264,7 +2261,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -2272,7 +2269,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -2280,7 +2277,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2288,7 +2285,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -2296,7 +2293,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -2304,7 +2301,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -2312,7 +2309,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -2320,7 +2317,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -2328,7 +2325,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2336,7 +2333,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2344,7 +2341,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -2352,7 +2349,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2360,7 +2357,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2368,7 +2365,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -2376,7 +2373,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -2384,7 +2381,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -2392,7 +2389,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -2400,7 +2397,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -2408,7 +2405,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -2416,7 +2413,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -2424,7 +2421,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -2432,7 +2429,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -2440,7 +2437,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -2448,7 +2445,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -2456,7 +2453,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -2464,7 +2461,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -2472,7 +2469,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -2480,7 +2477,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -2488,7 +2485,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -2496,7 +2493,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -2504,7 +2501,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -2512,7 +2509,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -2520,7 +2517,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -2528,7 +2525,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -2536,7 +2533,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -2544,7 +2541,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -2552,7 +2549,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -2560,7 +2557,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -2568,7 +2565,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -2576,7 +2573,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -2584,7 +2581,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -2592,7 +2589,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -2600,7 +2597,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -2608,7 +2605,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -2616,7 +2613,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -2624,7 +2621,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -2632,7 +2629,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -2640,7 +2637,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -2648,7 +2645,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -2656,7 +2653,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/divFME/ages/nya_ages/common_tabeller.xlsx
+++ b/divFME/ages/nya_ages/common_tabeller.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\kix\divFME\ages\nya_ages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEACD3D4-ABB9-468E-8C3F-9077373895E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E551B4-38A5-438A-A308-390CF1AA92FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="koordsys" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="193">
   <si>
     <t>Enköping lokala</t>
   </si>
@@ -609,13 +609,19 @@
   </si>
   <si>
     <t>beskrivning</t>
+  </si>
+  <si>
+    <t>Malmö museer</t>
+  </si>
+  <si>
+    <t>Mapinfo tab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -625,6 +631,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -650,8 +664,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1654,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.140625" customWidth="1"/>
@@ -1712,6 +1727,14 @@
         <v>71</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1719,13 +1742,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="72.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>47</v>
       </c>
@@ -1736,7 +1759,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1744,7 +1767,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1752,7 +1775,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1760,7 +1783,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1768,7 +1791,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1776,7 +1799,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1784,7 +1807,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1792,7 +1815,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1800,15 +1823,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1816,7 +1840,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1824,7 +1848,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1832,7 +1856,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1840,7 +1864,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1848,7 +1872,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2654,6 +2678,14 @@
       </c>
       <c r="B116" t="s">
         <v>186</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
